--- a/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
+++ b/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
@@ -199,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -656,11 +656,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -843,6 +858,41 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1168,12 +1218,6 @@
           <t>Legacy Diagnostics Client Roster</t>
         </is>
       </c>
-      <c r="B1" s="15" t="n"/>
-      <c r="C1" s="15" t="n"/>
-      <c r="D1" s="15" t="n"/>
-      <c r="E1" s="15" t="n"/>
-      <c r="F1" s="15" t="n"/>
-      <c r="G1" s="15" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
@@ -1181,16 +1225,16 @@
           <t>Owner:</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="82" t="inlineStr">
         <is>
           <t>Linh Vuong, Compliance &amp; Legal Counsel — Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="17" t="n"/>
-      <c r="E2" s="17" t="n"/>
-      <c r="F2" s="17" t="n"/>
-      <c r="G2" s="18" t="n"/>
+      <c r="C2" s="64" t="n"/>
+      <c r="D2" s="64" t="n"/>
+      <c r="E2" s="64" t="n"/>
+      <c r="F2" s="64" t="n"/>
+      <c r="G2" s="65" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
@@ -1198,16 +1242,12 @@
           <t>Companion policy:</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="83" t="inlineStr">
         <is>
           <t>Compliance Reserve &amp; Claims-Review Policy (09/15/2025)</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="21" t="n"/>
+      <c r="G3" s="66" t="n"/>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
@@ -1215,16 +1255,12 @@
           <t>Purpose:</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="84" t="inlineStr">
         <is>
           <t>Standing roster of regulated (diagnostics / instrumentation) accounts, both Thornfield-native and Inherited — Bramwell, used by Marketing Operations, Creative, and Finance to determine whether an account falls within scope of the Section 3 claims-review gate. Latest Claims Review Approval Date reflects the most recent Compliance-cleared claim on the sign-off log for the named account; it does not reflect Creative approval status.</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n"/>
-      <c r="D4" s="23" t="n"/>
-      <c r="E4" s="23" t="n"/>
-      <c r="F4" s="23" t="n"/>
-      <c r="G4" s="24" t="n"/>
+      <c r="G4" s="66" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -1232,16 +1268,16 @@
           <t>Last updated:</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>01/12/2026</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="27" t="n"/>
+      <c r="C5" s="67" t="n"/>
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="68" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1"/>
     <row r="7" ht="32" customHeight="1">
@@ -1312,7 +1348,7 @@
       </c>
       <c r="G8" s="36" t="inlineStr">
         <is>
-          <t>Thornfield native. Brief_v1.3 for the Q1 2026 launch received Creative approval on 12/18/2025 under the A25 doc-control log; no claims-review sign-off has been issued on any newer brief version for this campaign. Latest cleared claim on file remains the 09/22/2025 sensitivity-language approval from the prior campaign cycle.</t>
+          <t>Thornfield native. Brief_v1.3 for the Q1 2026 launch received Creative approval on 12/18/2025 under the Creative Brief Doc-Control Log; no claims-review sign-off has been issued on any newer brief version for this campaign. Latest cleared claim on file remains the 09/22/2025 sensitivity-language approval from the prior campaign cycle.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1535,7 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Vanmeer Analytical</t>
+          <t>Prescott Biosystems</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -1522,7 +1558,7 @@
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>Thornfield native. Category-norm claim cleared with peer-reviewed citation on file.</t>
+          <t>Inherited — Bramwell. Category-norm claim cleared with peer-reviewed citation on file.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1605,7 @@
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>Kestrelburg Reagents &amp; Diagnostics</t>
+          <t>Coleridge Biotech Marketing</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -1837,7 +1873,7 @@
       </c>
       <c r="G23" s="43" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell. First post-close claims-review clearance issued 09/15/2025 concurrent with policy effective date.</t>
+          <t>Thornfield native. First post-close claims-review clearance issued 09/15/2025 concurrent with policy effective date.</t>
         </is>
       </c>
     </row>
@@ -1996,25 +2032,65 @@
           <t>CUST-2025-0016</t>
         </is>
       </c>
-      <c r="B29" s="38" t="n"/>
-      <c r="C29" s="39" t="n"/>
-      <c r="D29" s="62" t="n"/>
-      <c r="E29" s="41" t="n"/>
+      <c r="B29" s="38" t="inlineStr">
+        <is>
+          <t>Brackenwood Diagnostics</t>
+        </is>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>Clinical diagnostics</t>
+        </is>
+      </c>
+      <c r="D29" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
       <c r="F29" s="45" t="n"/>
-      <c r="G29" s="43" t="n"/>
+      <c r="G29" s="43" t="inlineStr">
+        <is>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>CUST-2025-0037</t>
         </is>
       </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="61" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="46" t="n"/>
-      <c r="G30" s="36" t="n"/>
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>Steeplechase Diagnostics</t>
+        </is>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>In-vitro diagnostics</t>
+        </is>
+      </c>
+      <c r="D30" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
+      <c r="F30" s="45" t="n"/>
+      <c r="G30" s="43" t="inlineStr">
+        <is>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="37" t="inlineStr">
@@ -2022,25 +2098,65 @@
           <t>CUST-2025-0063</t>
         </is>
       </c>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="62" t="n"/>
-      <c r="E31" s="41" t="n"/>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>Palliser Diagnostics</t>
+        </is>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>Molecular diagnostics</t>
+        </is>
+      </c>
+      <c r="D31" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
       <c r="F31" s="45" t="n"/>
-      <c r="G31" s="43" t="n"/>
+      <c r="G31" s="43" t="inlineStr">
+        <is>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>CUST-2025-0075</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="61" t="n"/>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="36" t="n"/>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>Cornhill Diagnostics</t>
+        </is>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>Clinical diagnostics</t>
+        </is>
+      </c>
+      <c r="D32" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
+      <c r="F32" s="45" t="n"/>
+      <c r="G32" s="43" t="inlineStr">
+        <is>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="37" t="inlineStr">
@@ -2076,21 +2192,37 @@
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>CUST-2025-0118</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>Radstock Diagnostics</t>
         </is>
       </c>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="61" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="46" t="n"/>
-      <c r="G34" s="36" t="n"/>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>In-vitro diagnostics</t>
+        </is>
+      </c>
+      <c r="D34" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
+      <c r="F34" s="45" t="n"/>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="37" t="inlineStr">
@@ -2103,11 +2235,27 @@
           <t>Chatfield Diagnostics</t>
         </is>
       </c>
-      <c r="C35" s="39" t="n"/>
-      <c r="D35" s="62" t="n"/>
-      <c r="E35" s="41" t="n"/>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>Molecular diagnostics</t>
+        </is>
+      </c>
+      <c r="D35" s="62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>None currently in flight</t>
+        </is>
+      </c>
       <c r="F35" s="45" t="n"/>
-      <c r="G35" s="43" t="n"/>
+      <c r="G35" s="43" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="54" customHeight="1">
       <c r="A36" s="30" t="inlineStr">
@@ -2341,56 +2489,56 @@
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="47" t="inlineStr">
+      <c r="A43" s="71" t="inlineStr">
         <is>
           <t>Roster maintenance notes</t>
         </is>
       </c>
-      <c r="B43" s="48" t="n"/>
-      <c r="C43" s="48" t="n"/>
-      <c r="D43" s="48" t="n"/>
-      <c r="E43" s="48" t="n"/>
-      <c r="F43" s="48" t="n"/>
-      <c r="G43" s="49" t="n"/>
+      <c r="B43" s="72" t="n"/>
+      <c r="C43" s="72" t="n"/>
+      <c r="D43" s="72" t="n"/>
+      <c r="E43" s="72" t="n"/>
+      <c r="F43" s="72" t="n"/>
+      <c r="G43" s="73" t="n"/>
     </row>
     <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="50" t="inlineStr">
+      <c r="A44" s="74" t="inlineStr">
         <is>
           <t>Inclusion on this roster is governed by the client's regulated_client flag in ERPNext and by industry classification (in-vitro diagnostics, clinical diagnostics, molecular diagnostics, point-of-care diagnostics, veterinary diagnostics, laboratory instrumentation, analytical instrumentation, and bioinstrumentation). Removal requires written notice to Compliance. Marketing Operations and Creative should refresh their working copy from the erp.thornfieldlsm.com Customer master before staging any regulated-client creative for review.</t>
         </is>
       </c>
-      <c r="B44" s="51" t="n"/>
-      <c r="C44" s="51" t="n"/>
-      <c r="D44" s="51" t="n"/>
-      <c r="E44" s="51" t="n"/>
-      <c r="F44" s="51" t="n"/>
-      <c r="G44" s="52" t="n"/>
+      <c r="B44" s="75" t="n"/>
+      <c r="C44" s="75" t="n"/>
+      <c r="D44" s="75" t="n"/>
+      <c r="E44" s="75" t="n"/>
+      <c r="F44" s="75" t="n"/>
+      <c r="G44" s="76" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="53" t="inlineStr">
+      <c r="A45" s="77" t="inlineStr">
         <is>
           <t>The Latest Claims Review Approval Date column reflects the most recent entry for that client on the Compliance Sign-Off Log — Claims Review Approvals. It is not a substitute for the sign-off log itself, and a value in this column does not authorize distribution of a differently-worded claim or a later brief version. A cleared status attaches to the specific claim wording and creative version cleared, not to the client account as a whole.</t>
         </is>
       </c>
-      <c r="B45" s="54" t="n"/>
-      <c r="C45" s="54" t="n"/>
-      <c r="D45" s="54" t="n"/>
-      <c r="E45" s="54" t="n"/>
-      <c r="F45" s="54" t="n"/>
-      <c r="G45" s="55" t="n"/>
+      <c r="B45" s="69" t="n"/>
+      <c r="C45" s="69" t="n"/>
+      <c r="D45" s="69" t="n"/>
+      <c r="E45" s="69" t="n"/>
+      <c r="F45" s="69" t="n"/>
+      <c r="G45" s="78" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="56" t="inlineStr">
+      <c r="A46" s="79" t="inlineStr">
         <is>
           <t>Creative approval by the Creative Director (or delegate) under the doc-control log is a separate workflow from claims review. Where a brief version has been Creative-approved but contains a comparative or superiority claim for a regulated client on this roster, the shippable status of that version depends on whether the specific claim wording has been cleared through Compliance and logged on the sign-off log. Absence of an entry for a given wording means the claim has not cleared claims review.</t>
         </is>
       </c>
-      <c r="B46" s="57" t="n"/>
-      <c r="C46" s="57" t="n"/>
-      <c r="D46" s="57" t="n"/>
-      <c r="E46" s="57" t="n"/>
-      <c r="F46" s="57" t="n"/>
-      <c r="G46" s="58" t="n"/>
+      <c r="B46" s="80" t="n"/>
+      <c r="C46" s="80" t="n"/>
+      <c r="D46" s="80" t="n"/>
+      <c r="E46" s="80" t="n"/>
+      <c r="F46" s="80" t="n"/>
+      <c r="G46" s="81" t="n"/>
     </row>
     <row r="47" ht="12" customHeight="1"/>
     <row r="48" ht="20" customHeight="1">
@@ -2428,19 +2576,13 @@
       <c r="G49" s="60" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="9">
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="B34:G34"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:G5"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B35:G35"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A46:G46"/>

--- a/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
+++ b/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
@@ -1530,12 +1530,12 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>CUST-2025-0108</t>
+          <t>CUST-2025-0293</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Prescott Biosystems</t>
+          <t>Vanmeer Analytical</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell. Category-norm claim cleared with peer-reviewed citation on file.</t>
+          <t>Thornfield native. Category-norm claim cleared with peer-reviewed citation on file.</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F15" s="42" t="n">
-        <v>45908</v>
+        <v>45915</v>
       </c>
       <c r="G15" s="43" t="inlineStr">
         <is>

--- a/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
+++ b/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
@@ -2319,7 +2319,7 @@
       <c r="F37" s="45" t="n"/>
       <c r="G37" s="43" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       <c r="F38" s="46" t="n"/>
       <c r="G38" s="36" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
+          <t>Thornfield native. Roster entry created for claims-review screening coverage; no comparative claims currently in scope.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
+++ b/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G24" s="36" t="inlineStr">
         <is>
-          <t>Thornfield native. Co-branded creative reviewed under Section 3; distributor-side claims out of scope.</t>
+          <t>Inherited — Bramwell. Co-branded creative reviewed under Section 3; distributor-side claims out of scope.</t>
         </is>
       </c>
     </row>

--- a/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
+++ b/filesystem/Legal/Compliance/diagnostics_client_roster.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,6 +139,18 @@
       <color rgb="000284C7"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -675,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -892,6 +904,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1333,7 +1354,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1368,7 +1389,7 @@
           <t>Molecular diagnostics (PCR panels)</t>
         </is>
       </c>
-      <c r="D9" s="62" t="inlineStr">
+      <c r="D9" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1403,7 +1424,7 @@
           <t>In-vitro diagnostics (immunoassay)</t>
         </is>
       </c>
-      <c r="D10" s="61" t="inlineStr">
+      <c r="D10" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1438,7 +1459,7 @@
           <t>Clinical chemistry diagnostics</t>
         </is>
       </c>
-      <c r="D11" s="62" t="inlineStr">
+      <c r="D11" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1473,7 +1494,7 @@
           <t>Laboratory instrumentation (mass spec)</t>
         </is>
       </c>
-      <c r="D12" s="61" t="inlineStr">
+      <c r="D12" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1508,7 +1529,7 @@
           <t>Point-of-care diagnostics</t>
         </is>
       </c>
-      <c r="D13" s="62" t="inlineStr">
+      <c r="D13" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1543,7 +1564,7 @@
           <t>Analytical instrumentation</t>
         </is>
       </c>
-      <c r="D14" s="61" t="inlineStr">
+      <c r="D14" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1578,7 +1599,7 @@
           <t>In-vitro diagnostics (autoimmune)</t>
         </is>
       </c>
-      <c r="D15" s="62" t="inlineStr">
+      <c r="D15" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1613,7 +1634,7 @@
           <t>Diagnostics reagents &amp; controls</t>
         </is>
       </c>
-      <c r="D16" s="61" t="inlineStr">
+      <c r="D16" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1648,7 +1669,7 @@
           <t>Clinical diagnostics platforms</t>
         </is>
       </c>
-      <c r="D17" s="62" t="inlineStr">
+      <c r="D17" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1683,7 +1704,7 @@
           <t>Laboratory instrumentation OEM</t>
         </is>
       </c>
-      <c r="D18" s="61" t="inlineStr">
+      <c r="D18" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1718,7 +1739,7 @@
           <t>Bioinstrumentation (imaging)</t>
         </is>
       </c>
-      <c r="D19" s="62" t="inlineStr">
+      <c r="D19" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1753,7 +1774,7 @@
           <t>Molecular diagnostics (NGS)</t>
         </is>
       </c>
-      <c r="D20" s="61" t="inlineStr">
+      <c r="D20" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1788,7 +1809,7 @@
           <t>Clinical diagnostics platforms</t>
         </is>
       </c>
-      <c r="D21" s="62" t="inlineStr">
+      <c r="D21" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1823,7 +1844,7 @@
           <t>In-vitro diagnostics (infectious disease)</t>
         </is>
       </c>
-      <c r="D22" s="61" t="inlineStr">
+      <c r="D22" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1838,7 +1859,7 @@
       </c>
       <c r="G22" s="36" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell. Claim "clinically validated across [n] sites" cleared with study citation.</t>
+          <t>Inherited — Bramwell. Claim "clinically validated across 14 clinical sites" cleared with study citation.</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1879,7 @@
           <t>Laboratory instrumentation (hematology)</t>
         </is>
       </c>
-      <c r="D23" s="62" t="inlineStr">
+      <c r="D23" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1893,7 +1914,7 @@
           <t>Diagnostics distribution &amp; branded assays</t>
         </is>
       </c>
-      <c r="D24" s="61" t="inlineStr">
+      <c r="D24" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1928,7 +1949,7 @@
           <t>Analytical instrumentation (chromatography)</t>
         </is>
       </c>
-      <c r="D25" s="62" t="inlineStr">
+      <c r="D25" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1963,7 +1984,7 @@
           <t>Veterinary diagnostics</t>
         </is>
       </c>
-      <c r="D26" s="61" t="inlineStr">
+      <c r="D26" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1998,7 +2019,7 @@
           <t>Bio-analytical instrumentation</t>
         </is>
       </c>
-      <c r="D27" s="62" t="inlineStr">
+      <c r="D27" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2042,7 +2063,7 @@
           <t>Clinical diagnostics</t>
         </is>
       </c>
-      <c r="D29" s="62" t="inlineStr">
+      <c r="D29" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2075,7 +2096,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D30" s="62" t="inlineStr">
+      <c r="D30" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2108,7 +2129,7 @@
           <t>Molecular diagnostics</t>
         </is>
       </c>
-      <c r="D31" s="62" t="inlineStr">
+      <c r="D31" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2141,7 +2162,7 @@
           <t>Clinical diagnostics</t>
         </is>
       </c>
-      <c r="D32" s="62" t="inlineStr">
+      <c r="D32" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2174,7 +2195,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D33" s="62" t="inlineStr">
+      <c r="D33" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2207,7 +2228,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D34" s="62" t="inlineStr">
+      <c r="D34" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2240,7 +2261,7 @@
           <t>Molecular diagnostics</t>
         </is>
       </c>
-      <c r="D35" s="62" t="inlineStr">
+      <c r="D35" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2273,7 +2294,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D36" s="61" t="inlineStr">
+      <c r="D36" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2306,7 +2327,7 @@
           <t>Molecular diagnostics</t>
         </is>
       </c>
-      <c r="D37" s="62" t="inlineStr">
+      <c r="D37" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2339,7 +2360,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D38" s="61" t="inlineStr">
+      <c r="D38" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2372,7 +2393,7 @@
           <t>Clinical diagnostics</t>
         </is>
       </c>
-      <c r="D39" s="62" t="inlineStr">
+      <c r="D39" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2405,7 +2426,7 @@
           <t>Clinical diagnostics</t>
         </is>
       </c>
-      <c r="D40" s="61" t="inlineStr">
+      <c r="D40" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2438,7 +2459,7 @@
           <t>Molecular diagnostics</t>
         </is>
       </c>
-      <c r="D41" s="62" t="inlineStr">
+      <c r="D41" s="86" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2471,7 +2492,7 @@
           <t>In-vitro diagnostics</t>
         </is>
       </c>
-      <c r="D42" s="61" t="inlineStr">
+      <c r="D42" s="85" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2542,7 +2563,7 @@
     </row>
     <row r="47" ht="12" customHeight="1"/>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="59" t="inlineStr">
+      <c r="A48" s="87" t="inlineStr">
         <is>
           <t>Prepared and maintained by:</t>
         </is>
@@ -2559,7 +2580,7 @@
       <c r="G48" s="60" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="59" t="inlineStr">
+      <c r="A49" s="87" t="inlineStr">
         <is>
           <t>Last updated:</t>
         </is>
